--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd3b1d5e40ccc487c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rffc0e8c373ba4126"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rffc0e8c373ba4126"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R78f00b00d5ed4cfd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R78f00b00d5ed4cfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R80eedc86ff704a3c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R80eedc86ff704a3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4dc36b5313bd4b4b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4dc36b5313bd4b4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b67d9e9871b49ce"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b67d9e9871b49ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R31784abf0d13440d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R31784abf0d13440d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd28300ba3a2448a9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd28300ba3a2448a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdbc7dbe007b44f11"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdbc7dbe007b44f11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R04eaeb4ea863475b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R04eaeb4ea863475b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra214a1ca6c364c68"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra214a1ca6c364c68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2697acf379d34954"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2697acf379d34954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69f48f5698d149c7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69f48f5698d149c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd913116faae944eb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd913116faae944eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfe49894b68804ea0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TextNumberBooleanDateCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfe49894b68804ea0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdf4b8df15b134321"/>
   </x:sheets>
 </x:workbook>
 </file>
